--- a/datos/valido_A_V.xlsx
+++ b/datos/valido_A_V.xlsx
@@ -438,10 +438,10 @@
         <v>-1</v>
       </c>
       <c r="B2" t="n">
-        <v>-9.609466342471258e-07</v>
+        <v>-7.91382815628556e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5748750166351512</v>
+        <v>0.8597657465422806</v>
       </c>
     </row>
     <row r="3">
@@ -449,10 +449,10 @@
         <v>-0.9797979797979798</v>
       </c>
       <c r="B3" t="n">
-        <v>-8.765908255705199e-07</v>
+        <v>-9.535556356896187e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6897763395651223</v>
+        <v>0.5655009916061121</v>
       </c>
     </row>
     <row r="4">
@@ -460,10 +460,10 @@
         <v>-0.9595959595959596</v>
       </c>
       <c r="B4" t="n">
-        <v>-7.955653179906786e-07</v>
+        <v>-1.131456109963461e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9970579625822681</v>
+        <v>0.9956488281528918</v>
       </c>
     </row>
     <row r="5">
@@ -471,10 +471,10 @@
         <v>-0.9393939393939394</v>
       </c>
       <c r="B5" t="n">
-        <v>-9.50773373103637e-07</v>
+        <v>-1.004443860545327e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>0.598268983471989</v>
+        <v>0.3657040435596536</v>
       </c>
     </row>
     <row r="6">
@@ -482,10 +482,10 @@
         <v>-0.9191919191919192</v>
       </c>
       <c r="B6" t="n">
-        <v>-9.766191629732724e-07</v>
+        <v>-1.123865225013688e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9906671821606348</v>
+        <v>0.7019497334496633</v>
       </c>
     </row>
     <row r="7">
@@ -493,10 +493,10 @@
         <v>-0.898989898989899</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.092089404279077e-06</v>
+        <v>-9.884863891399779e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5049671328790927</v>
+        <v>0.5409879100332022</v>
       </c>
     </row>
     <row r="8">
@@ -504,10 +504,10 @@
         <v>-0.8787878787878788</v>
       </c>
       <c r="B8" t="n">
-        <v>-9.009967291394586e-07</v>
+        <v>-1.01318190063276e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8443115551934192</v>
+        <v>0.4309893385014196</v>
       </c>
     </row>
     <row r="9">
@@ -515,10 +515,10 @@
         <v>-0.8585858585858586</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.029681632173676e-06</v>
+        <v>-1.003495655064162e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01660448705876272</v>
+        <v>0.3168468471363356</v>
       </c>
     </row>
     <row r="10">
@@ -526,10 +526,10 @@
         <v>-0.8383838383838383</v>
       </c>
       <c r="B10" t="n">
-        <v>-9.123152119783351e-07</v>
+        <v>-9.000748826094709e-07</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8330952530486943</v>
+        <v>0.1998943209466705</v>
       </c>
     </row>
     <row r="11">
@@ -537,10 +537,10 @@
         <v>-0.8181818181818181</v>
       </c>
       <c r="B11" t="n">
-        <v>-8.306896515828647e-07</v>
+        <v>-1.032605925694341e-06</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1200999545909719</v>
+        <v>0.494717919375517</v>
       </c>
     </row>
     <row r="12">
@@ -548,10 +548,10 @@
         <v>-0.797979797979798</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.044910658503084e-06</v>
+        <v>-1.185632518580231e-06</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8345832822838801</v>
+        <v>0.8567564858344039</v>
       </c>
     </row>
     <row r="13">
@@ -559,10 +559,10 @@
         <v>-0.7777777777777778</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.185597067792093e-06</v>
+        <v>-1.088475544188018e-06</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5807941987209437</v>
+        <v>0.9664678332564142</v>
       </c>
     </row>
     <row r="14">
@@ -570,10 +570,10 @@
         <v>-0.7575757575757576</v>
       </c>
       <c r="B14" t="n">
-        <v>-8.695200962229845e-07</v>
+        <v>-1.046282513347392e-06</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8227531403075301</v>
+        <v>0.09707694792436261</v>
       </c>
     </row>
     <row r="15">
@@ -581,10 +581,10 @@
         <v>-0.7373737373737373</v>
       </c>
       <c r="B15" t="n">
-        <v>-1.005159786859004e-06</v>
+        <v>-1.039953389881279e-06</v>
       </c>
       <c r="C15" t="n">
-        <v>0.910470520068452</v>
+        <v>0.01039690385540026</v>
       </c>
     </row>
     <row r="16">
@@ -592,10 +592,10 @@
         <v>-0.7171717171717171</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.044403699694777e-06</v>
+        <v>-1.058303790315129e-06</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1634610778170814</v>
+        <v>0.3301078506035493</v>
       </c>
     </row>
     <row r="17">
@@ -603,10 +603,10 @@
         <v>-0.696969696969697</v>
       </c>
       <c r="B17" t="n">
-        <v>-8.669110647723118e-07</v>
+        <v>-1.033541358240666e-06</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5596323147360812</v>
+        <v>0.9180238196886684</v>
       </c>
     </row>
     <row r="18">
@@ -614,10 +614,10 @@
         <v>-0.6767676767676767</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.032630926241096e-06</v>
+        <v>-1.006585056017597e-06</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3691706952542142</v>
+        <v>0.1709039759092371</v>
       </c>
     </row>
     <row r="19">
@@ -625,10 +625,10 @@
         <v>-0.6565656565656566</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.056996854873408e-06</v>
+        <v>-1.059339781256684e-06</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4337191971050174</v>
+        <v>0.06317591700204628</v>
       </c>
     </row>
     <row r="20">
@@ -636,10 +636,10 @@
         <v>-0.6363636363636364</v>
       </c>
       <c r="B20" t="n">
-        <v>-9.440384584723376e-07</v>
+        <v>-9.969655743174341e-07</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5761596775005777</v>
+        <v>0.607328476610774</v>
       </c>
     </row>
     <row r="21">
@@ -647,10 +647,10 @@
         <v>-0.6161616161616161</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.004059954269459e-06</v>
+        <v>-8.543447378966739e-07</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7432296055047886</v>
+        <v>0.06855063292951868</v>
       </c>
     </row>
     <row r="22">
@@ -658,10 +658,10 @@
         <v>-0.5959595959595959</v>
       </c>
       <c r="B22" t="n">
-        <v>-1.1526620529608e-06</v>
+        <v>-9.36014181879687e-07</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2337963773140571</v>
+        <v>0.4451886051518361</v>
       </c>
     </row>
     <row r="23">
@@ -669,10 +669,10 @@
         <v>-0.5757575757575757</v>
       </c>
       <c r="B23" t="n">
-        <v>-9.968145941684345e-07</v>
+        <v>-8.601049299330769e-07</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9665445466442824</v>
+        <v>0.6738111832154418</v>
       </c>
     </row>
     <row r="24">
@@ -680,10 +680,10 @@
         <v>-0.5555555555555556</v>
       </c>
       <c r="B24" t="n">
-        <v>-8.992346674581309e-07</v>
+        <v>-1.119439146697948e-06</v>
       </c>
       <c r="C24" t="n">
-        <v>0.07178695061893758</v>
+        <v>0.5525194095288835</v>
       </c>
     </row>
     <row r="25">
@@ -691,10 +691,10 @@
         <v>-0.5353535353535352</v>
       </c>
       <c r="B25" t="n">
-        <v>-9.540038580543771e-07</v>
+        <v>-8.505279430467819e-07</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6032109272523717</v>
+        <v>0.1579124141312841</v>
       </c>
     </row>
     <row r="26">
@@ -702,10 +702,10 @@
         <v>-0.5151515151515151</v>
       </c>
       <c r="B26" t="n">
-        <v>-1.132195649329711e-06</v>
+        <v>-9.48465417546847e-07</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4678461322666829</v>
+        <v>0.9752332546535737</v>
       </c>
     </row>
     <row r="27">
@@ -713,10 +713,10 @@
         <v>-0.4949494949494949</v>
       </c>
       <c r="B27" t="n">
-        <v>-1.144214314640951e-06</v>
+        <v>-8.255663568746406e-07</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8590870977292233</v>
+        <v>0.6846797383111051</v>
       </c>
     </row>
     <row r="28">
@@ -724,10 +724,10 @@
         <v>-0.4747474747474747</v>
       </c>
       <c r="B28" t="n">
-        <v>-1.077646461219342e-06</v>
+        <v>-1.066192118224432e-06</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3452622001649974</v>
+        <v>0.37456112122695</v>
       </c>
     </row>
     <row r="29">
@@ -735,10 +735,10 @@
         <v>-0.4545454545454545</v>
       </c>
       <c r="B29" t="n">
-        <v>-1.020112747435196e-06</v>
+        <v>-8.71602550749342e-07</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2094310525729359</v>
+        <v>0.2490038526117699</v>
       </c>
     </row>
     <row r="30">
@@ -746,10 +746,10 @@
         <v>-0.4343434343434343</v>
       </c>
       <c r="B30" t="n">
-        <v>-9.225494856553427e-07</v>
+        <v>-9.416885733387146e-07</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1570535299674906</v>
+        <v>0.4700082882592929</v>
       </c>
     </row>
     <row r="31">
@@ -757,10 +757,10 @@
         <v>-0.4141414141414141</v>
       </c>
       <c r="B31" t="n">
-        <v>-9.58871398584576e-07</v>
+        <v>-1.140816881680844e-06</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3644461469133062</v>
+        <v>0.9576465876456245</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         <v>-0.3939393939393939</v>
       </c>
       <c r="B32" t="n">
-        <v>-1.010253579674973e-06</v>
+        <v>-9.541626860037162e-07</v>
       </c>
       <c r="C32" t="n">
-        <v>0.681545663366856</v>
+        <v>0.7015172912985294</v>
       </c>
     </row>
     <row r="33">
@@ -779,10 +779,10 @@
         <v>-0.3737373737373737</v>
       </c>
       <c r="B33" t="n">
-        <v>-9.35990897124908e-07</v>
+        <v>-1.139045401304021e-06</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7473631997442178</v>
+        <v>0.9374548021764972</v>
       </c>
     </row>
     <row r="34">
@@ -790,10 +790,10 @@
         <v>-0.3535353535353535</v>
       </c>
       <c r="B34" t="n">
-        <v>-1.102311305505434e-06</v>
+        <v>-8.850531152068297e-07</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5067565040833085</v>
+        <v>0.3257677724655811</v>
       </c>
     </row>
     <row r="35">
@@ -801,10 +801,10 @@
         <v>-0.3333333333333333</v>
       </c>
       <c r="B35" t="n">
-        <v>-1.013439676822753e-06</v>
+        <v>-9.308071163259937e-07</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2329060141354926</v>
+        <v>0.1671781059806727</v>
       </c>
     </row>
     <row r="36">
@@ -812,10 +812,10 @@
         <v>-0.313131313131313</v>
       </c>
       <c r="B36" t="n">
-        <v>-9.073113497869711e-07</v>
+        <v>-9.199858250862126e-07</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6004776383706479</v>
+        <v>0.3896009606275819</v>
       </c>
     </row>
     <row r="37">
@@ -823,10 +823,10 @@
         <v>-0.2929292929292928</v>
       </c>
       <c r="B37" t="n">
-        <v>-9.470445996478943e-07</v>
+        <v>-1.074826770891062e-06</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4661057099325182</v>
+        <v>0.2545174802438227</v>
       </c>
     </row>
     <row r="38">
@@ -834,10 +834,10 @@
         <v>-0.2727272727272727</v>
       </c>
       <c r="B38" t="n">
-        <v>-8.631472804968807e-07</v>
+        <v>-1.016937329730066e-06</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9948808636737637</v>
+        <v>0.6392434461088895</v>
       </c>
     </row>
     <row r="39">
@@ -845,10 +845,10 @@
         <v>-0.2525252525252525</v>
       </c>
       <c r="B39" t="n">
-        <v>-9.97554825477022e-07</v>
+        <v>-8.673856374865777e-07</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3714452789500918</v>
+        <v>0.1266600229626923</v>
       </c>
     </row>
     <row r="40">
@@ -856,10 +856,10 @@
         <v>-0.2323232323232323</v>
       </c>
       <c r="B40" t="n">
-        <v>-9.475758882702632e-07</v>
+        <v>-7.82584376595757e-07</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6191812141495312</v>
+        <v>0.3972461762124689</v>
       </c>
     </row>
     <row r="41">
@@ -867,10 +867,10 @@
         <v>-0.212121212121212</v>
       </c>
       <c r="B41" t="n">
-        <v>-8.22917474985072e-07</v>
+        <v>-7.758090387364335e-07</v>
       </c>
       <c r="C41" t="n">
-        <v>0.05248923933756955</v>
+        <v>0.6929457587636271</v>
       </c>
     </row>
     <row r="42">
@@ -878,10 +878,10 @@
         <v>-0.1919191919191918</v>
       </c>
       <c r="B42" t="n">
-        <v>-8.615798047460888e-07</v>
+        <v>-8.895480824425226e-07</v>
       </c>
       <c r="C42" t="n">
-        <v>0.006141169437491101</v>
+        <v>0.4843620132252346</v>
       </c>
     </row>
     <row r="43">
@@ -889,10 +889,10 @@
         <v>-0.1717171717171716</v>
       </c>
       <c r="B43" t="n">
-        <v>-9.145516778840319e-07</v>
+        <v>-8.175269900738015e-07</v>
       </c>
       <c r="C43" t="n">
-        <v>0.6393994550694754</v>
+        <v>0.5270199758905224</v>
       </c>
     </row>
     <row r="44">
@@ -900,10 +900,10 @@
         <v>-0.1515151515151515</v>
       </c>
       <c r="B44" t="n">
-        <v>-7.624230509256194e-07</v>
+        <v>-7.288944401382436e-07</v>
       </c>
       <c r="C44" t="n">
-        <v>0.05711385641419442</v>
+        <v>0.03428083918255065</v>
       </c>
     </row>
     <row r="45">
@@ -911,10 +911,10 @@
         <v>-0.1313131313131313</v>
       </c>
       <c r="B45" t="n">
-        <v>-7.394325141980303e-07</v>
+        <v>-6.715202624589571e-07</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2842238392987688</v>
+        <v>0.4015712841660963</v>
       </c>
     </row>
     <row r="46">
@@ -922,10 +922,10 @@
         <v>-0.111111111111111</v>
       </c>
       <c r="B46" t="n">
-        <v>-7.948276533872205e-07</v>
+        <v>-5.742423216936066e-07</v>
       </c>
       <c r="C46" t="n">
-        <v>0.4987861593891768</v>
+        <v>0.8527263858048503</v>
       </c>
     </row>
     <row r="47">
@@ -933,10 +933,10 @@
         <v>-0.09090909090909083</v>
       </c>
       <c r="B47" t="n">
-        <v>-5.691423605617359e-07</v>
+        <v>-6.246510214054008e-07</v>
       </c>
       <c r="C47" t="n">
-        <v>0.06873087864447702</v>
+        <v>0.415112063522022</v>
       </c>
     </row>
     <row r="48">
@@ -944,10 +944,10 @@
         <v>-0.07070707070707061</v>
       </c>
       <c r="B48" t="n">
-        <v>-4.529736703064663e-07</v>
+        <v>-2.823514400274572e-07</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5964403911758848</v>
+        <v>0.556244513823373</v>
       </c>
     </row>
     <row r="49">
@@ -955,10 +955,10 @@
         <v>-0.05050505050505039</v>
       </c>
       <c r="B49" t="n">
-        <v>-4.970012638879076e-07</v>
+        <v>-3.446189635583563e-07</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4308381576612585</v>
+        <v>0.8013892896228683</v>
       </c>
     </row>
     <row r="50">
@@ -966,10 +966,10 @@
         <v>-0.03030303030303028</v>
       </c>
       <c r="B50" t="n">
-        <v>-5.443539253830641e-07</v>
+        <v>-1.983740232388145e-07</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6451858693578414</v>
+        <v>0.3388577075917287</v>
       </c>
     </row>
     <row r="51">
@@ -977,10 +977,10 @@
         <v>-0.01010101010101006</v>
       </c>
       <c r="B51" t="n">
-        <v>-3.924635569501235e-08</v>
+        <v>-8.830992649268545e-08</v>
       </c>
       <c r="C51" t="n">
-        <v>0.6711677746929741</v>
+        <v>0.09096822682718064</v>
       </c>
     </row>
     <row r="52">
@@ -988,10 +988,10 @@
         <v>0.01010101010101017</v>
       </c>
       <c r="B52" t="n">
-        <v>1.108185199119697e-07</v>
+        <v>1.429669107922869e-07</v>
       </c>
       <c r="C52" t="n">
-        <v>0.950049938786004</v>
+        <v>0.3681495628310731</v>
       </c>
     </row>
     <row r="53">
@@ -999,10 +999,10 @@
         <v>0.0303030303030305</v>
       </c>
       <c r="B53" t="n">
-        <v>3.835065771896282e-07</v>
+        <v>4.714843374497352e-07</v>
       </c>
       <c r="C53" t="n">
-        <v>0.6701933392159347</v>
+        <v>0.756758935001796</v>
       </c>
     </row>
     <row r="54">
@@ -1010,10 +1010,10 @@
         <v>0.05050505050505061</v>
       </c>
       <c r="B54" t="n">
-        <v>4.907672278348197e-07</v>
+        <v>7.826311561243153e-07</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7404168377914649</v>
+        <v>0.5715742839994177</v>
       </c>
     </row>
     <row r="55">
@@ -1021,10 +1021,10 @@
         <v>0.07070707070707072</v>
       </c>
       <c r="B55" t="n">
-        <v>1.105272760305219e-06</v>
+        <v>1.127508592491403e-06</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7040002658510995</v>
+        <v>0.7816706896164148</v>
       </c>
     </row>
     <row r="56">
@@ -1032,10 +1032,10 @@
         <v>0.09090909090909105</v>
       </c>
       <c r="B56" t="n">
-        <v>1.637256880438084e-06</v>
+        <v>1.618874982278266e-06</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5121756839781169</v>
+        <v>0.8032107108000118</v>
       </c>
     </row>
     <row r="57">
@@ -1043,10 +1043,10 @@
         <v>0.1111111111111112</v>
       </c>
       <c r="B57" t="n">
-        <v>1.859869206435342e-06</v>
+        <v>2.220029517814765e-06</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7509491067268259</v>
+        <v>0.5823380218450851</v>
       </c>
     </row>
     <row r="58">
@@ -1054,10 +1054,10 @@
         <v>0.1313131313131315</v>
       </c>
       <c r="B58" t="n">
-        <v>2.621121182018438e-06</v>
+        <v>2.656409118615374e-06</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9868285916946747</v>
+        <v>0.01986163574362187</v>
       </c>
     </row>
     <row r="59">
@@ -1065,10 +1065,10 @@
         <v>0.1515151515151516</v>
       </c>
       <c r="B59" t="n">
-        <v>3.440949344063233e-06</v>
+        <v>3.714190637854328e-06</v>
       </c>
       <c r="C59" t="n">
-        <v>0.6237877812439964</v>
+        <v>0.2776228956103163</v>
       </c>
     </row>
     <row r="60">
@@ -1076,10 +1076,10 @@
         <v>0.1717171717171717</v>
       </c>
       <c r="B60" t="n">
-        <v>4.641552677821315e-06</v>
+        <v>4.548723875859343e-06</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7993170793925131</v>
+        <v>0.204644714746124</v>
       </c>
     </row>
     <row r="61">
@@ -1087,10 +1087,10 @@
         <v>0.191919191919192</v>
       </c>
       <c r="B61" t="n">
-        <v>5.809032771210124e-06</v>
+        <v>5.786113609983416e-06</v>
       </c>
       <c r="C61" t="n">
-        <v>0.699044280520062</v>
+        <v>0.912724830375214</v>
       </c>
     </row>
     <row r="62">
@@ -1098,10 +1098,10 @@
         <v>0.2121212121212122</v>
       </c>
       <c r="B62" t="n">
-        <v>7.138929750091198e-06</v>
+        <v>7.209346273337599e-06</v>
       </c>
       <c r="C62" t="n">
-        <v>0.4227853598567788</v>
+        <v>0.3320408056737375</v>
       </c>
     </row>
     <row r="63">
@@ -1109,10 +1109,10 @@
         <v>0.2323232323232325</v>
       </c>
       <c r="B63" t="n">
-        <v>9.272984828563348e-06</v>
+        <v>9.206414237881108e-06</v>
       </c>
       <c r="C63" t="n">
-        <v>0.2986187614644794</v>
+        <v>0.4951326004181525</v>
       </c>
     </row>
     <row r="64">
@@ -1120,10 +1120,10 @@
         <v>0.2525252525252526</v>
       </c>
       <c r="B64" t="n">
-        <v>1.163099323360085e-05</v>
+        <v>1.156230839659215e-05</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6648628947579193</v>
+        <v>0.1590947244937484</v>
       </c>
     </row>
     <row r="65">
@@ -1131,10 +1131,10 @@
         <v>0.2727272727272729</v>
       </c>
       <c r="B65" t="n">
-        <v>1.433967378154525e-05</v>
+        <v>1.412338935635992e-05</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7139204336404665</v>
+        <v>0.7349339632640317</v>
       </c>
     </row>
     <row r="66">
@@ -1142,10 +1142,10 @@
         <v>0.292929292929293</v>
       </c>
       <c r="B66" t="n">
-        <v>1.788231805084302e-05</v>
+        <v>1.782310794917316e-05</v>
       </c>
       <c r="C66" t="n">
-        <v>0.2480517579328814</v>
+        <v>0.3036745902764156</v>
       </c>
     </row>
     <row r="67">
@@ -1153,10 +1153,10 @@
         <v>0.3131313131313131</v>
       </c>
       <c r="B67" t="n">
-        <v>2.185829782401345e-05</v>
+        <v>2.174355338043834e-05</v>
       </c>
       <c r="C67" t="n">
-        <v>0.8662802942004629</v>
+        <v>0.006755768081217917</v>
       </c>
     </row>
     <row r="68">
@@ -1164,10 +1164,10 @@
         <v>0.3333333333333335</v>
       </c>
       <c r="B68" t="n">
-        <v>2.698428448751635e-05</v>
+        <v>2.70193782797603e-05</v>
       </c>
       <c r="C68" t="n">
-        <v>0.03910720676491453</v>
+        <v>0.5702962702790336</v>
       </c>
     </row>
     <row r="69">
@@ -1175,10 +1175,10 @@
         <v>0.3535353535353536</v>
       </c>
       <c r="B69" t="n">
-        <v>3.311876051703009e-05</v>
+        <v>3.340512757349078e-05</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5048020357377609</v>
+        <v>0.1430199462240163</v>
       </c>
     </row>
     <row r="70">
@@ -1186,10 +1186,10 @@
         <v>0.3737373737373739</v>
       </c>
       <c r="B70" t="n">
-        <v>4.093800944478297e-05</v>
+        <v>4.095258448956087e-05</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7399221594205178</v>
+        <v>0.7172918345969204</v>
       </c>
     </row>
     <row r="71">
@@ -1197,10 +1197,10 @@
         <v>0.393939393939394</v>
       </c>
       <c r="B71" t="n">
-        <v>5.047216720658804e-05</v>
+        <v>5.037597661793206e-05</v>
       </c>
       <c r="C71" t="n">
-        <v>0.07191295978908852</v>
+        <v>0.8830115865071336</v>
       </c>
     </row>
     <row r="72">
@@ -1208,10 +1208,10 @@
         <v>0.4141414141414144</v>
       </c>
       <c r="B72" t="n">
-        <v>6.181956302355951e-05</v>
+        <v>6.202513172468231e-05</v>
       </c>
       <c r="C72" t="n">
-        <v>0.3812395897066193</v>
+        <v>0.5579769067668255</v>
       </c>
     </row>
     <row r="73">
@@ -1219,10 +1219,10 @@
         <v>0.4343434343434345</v>
       </c>
       <c r="B73" t="n">
-        <v>7.600796894892056e-05</v>
+        <v>7.604588860342151e-05</v>
       </c>
       <c r="C73" t="n">
-        <v>0.4374874802905463</v>
+        <v>0.8566704900485425</v>
       </c>
     </row>
     <row r="74">
@@ -1230,10 +1230,10 @@
         <v>0.4545454545454546</v>
       </c>
       <c r="B74" t="n">
-        <v>9.319905015588902e-05</v>
+        <v>9.316761245069294e-05</v>
       </c>
       <c r="C74" t="n">
-        <v>0.9224788563520148</v>
+        <v>0.6446452775340766</v>
       </c>
     </row>
     <row r="75">
@@ -1241,10 +1241,10 @@
         <v>0.4747474747474749</v>
       </c>
       <c r="B75" t="n">
-        <v>0.0001143815729528499</v>
+        <v>0.0001141109558667256</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6411204561381824</v>
+        <v>0.286852507569956</v>
       </c>
     </row>
     <row r="76">
@@ -1252,10 +1252,10 @@
         <v>0.494949494949495</v>
       </c>
       <c r="B76" t="n">
-        <v>0.0001399842252002913</v>
+        <v>0.0001400139975597575</v>
       </c>
       <c r="C76" t="n">
-        <v>0.2099897496576139</v>
+        <v>0.8036932903190454</v>
       </c>
     </row>
     <row r="77">
@@ -1263,10 +1263,10 @@
         <v>0.5151515151515154</v>
       </c>
       <c r="B77" t="n">
-        <v>0.0001715000718992064</v>
+        <v>0.0001716564061462679</v>
       </c>
       <c r="C77" t="n">
-        <v>0.9377581384238179</v>
+        <v>0.1243848018535424</v>
       </c>
     </row>
     <row r="78">
@@ -1274,10 +1274,10 @@
         <v>0.5353535353535355</v>
       </c>
       <c r="B78" t="n">
-        <v>0.000210325585866358</v>
+        <v>0.0002104265272911884</v>
       </c>
       <c r="C78" t="n">
-        <v>0.1013168446091878</v>
+        <v>0.1535736524106033</v>
       </c>
     </row>
     <row r="79">
@@ -1285,10 +1285,10 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="B79" t="n">
-        <v>0.0002576693047642591</v>
+        <v>0.0002577169137352468</v>
       </c>
       <c r="C79" t="n">
-        <v>0.6200475855896787</v>
+        <v>0.0381150762725061</v>
       </c>
     </row>
     <row r="80">
@@ -1296,10 +1296,10 @@
         <v>0.5757575757575759</v>
       </c>
       <c r="B80" t="n">
-        <v>0.0003156304770833025</v>
+        <v>0.0003153731223160003</v>
       </c>
       <c r="C80" t="n">
-        <v>0.8537544862307738</v>
+        <v>0.05293276426416549</v>
       </c>
     </row>
     <row r="81">
@@ -1307,10 +1307,10 @@
         <v>0.595959595959596</v>
       </c>
       <c r="B81" t="n">
-        <v>0.0003865037404361422</v>
+        <v>0.000386465786532845</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9192050676830795</v>
+        <v>0.01317163726587223</v>
       </c>
     </row>
     <row r="82">
@@ -1318,10 +1318,10 @@
         <v>0.6161616161616164</v>
       </c>
       <c r="B82" t="n">
-        <v>0.0004732390918885932</v>
+        <v>0.0004731496588571047</v>
       </c>
       <c r="C82" t="n">
-        <v>0.2382344561557972</v>
+        <v>0.5591079458747207</v>
       </c>
     </row>
     <row r="83">
@@ -1329,10 +1329,10 @@
         <v>0.6363636363636365</v>
       </c>
       <c r="B83" t="n">
-        <v>0.0005793717229572818</v>
+        <v>0.0005794097336626033</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7499035348348976</v>
+        <v>0.8837469288700445</v>
       </c>
     </row>
     <row r="84">
@@ -1340,10 +1340,10 @@
         <v>0.6565656565656568</v>
       </c>
       <c r="B84" t="n">
-        <v>0.0007092304378291847</v>
+        <v>0.0007091473019052056</v>
       </c>
       <c r="C84" t="n">
-        <v>0.4976680085878722</v>
+        <v>0.7611968666118378</v>
       </c>
     </row>
     <row r="85">
@@ -1351,10 +1351,10 @@
         <v>0.6767676767676769</v>
       </c>
       <c r="B85" t="n">
-        <v>0.0008682262470220052</v>
+        <v>0.0008683235530685728</v>
       </c>
       <c r="C85" t="n">
-        <v>0.4310822132125659</v>
+        <v>0.6576139506536023</v>
       </c>
     </row>
     <row r="86">
@@ -1362,10 +1362,10 @@
         <v>0.696969696969697</v>
       </c>
       <c r="B86" t="n">
-        <v>0.001062926641850615</v>
+        <v>0.001062811176163554</v>
       </c>
       <c r="C86" t="n">
-        <v>0.8114855565186095</v>
+        <v>0.994879194668267</v>
       </c>
     </row>
     <row r="87">
@@ -1373,10 +1373,10 @@
         <v>0.7171717171717173</v>
       </c>
       <c r="B87" t="n">
-        <v>0.001301193520493501</v>
+        <v>0.001301132545570505</v>
       </c>
       <c r="C87" t="n">
-        <v>0.719548619305746</v>
+        <v>0.9028074875200334</v>
       </c>
     </row>
     <row r="88">
@@ -1384,10 +1384,10 @@
         <v>0.7373737373737375</v>
       </c>
       <c r="B88" t="n">
-        <v>0.001592488990564637</v>
+        <v>0.001592643415091225</v>
       </c>
       <c r="C88" t="n">
-        <v>0.7826571276977498</v>
+        <v>0.0262062647514244</v>
       </c>
     </row>
     <row r="89">
@@ -1395,10 +1395,10 @@
         <v>0.7575757575757578</v>
       </c>
       <c r="B89" t="n">
-        <v>0.001949576512799495</v>
+        <v>0.001949425169978047</v>
       </c>
       <c r="C89" t="n">
-        <v>0.3783005939932701</v>
+        <v>0.5947989578117957</v>
       </c>
     </row>
     <row r="90">
@@ -1406,10 +1406,10 @@
         <v>0.7777777777777779</v>
       </c>
       <c r="B90" t="n">
-        <v>0.002386037424967805</v>
+        <v>0.002385794714233967</v>
       </c>
       <c r="C90" t="n">
-        <v>0.6095506189807927</v>
+        <v>0.9997835024627569</v>
       </c>
     </row>
     <row r="91">
@@ -1417,10 +1417,10 @@
         <v>0.7979797979797982</v>
       </c>
       <c r="B91" t="n">
-        <v>0.002920473974893802</v>
+        <v>0.00292043309995853</v>
       </c>
       <c r="C91" t="n">
-        <v>0.9139790932269993</v>
+        <v>0.4944229140889388</v>
       </c>
     </row>
     <row r="92">
@@ -1428,10 +1428,10 @@
         <v>0.8181818181818183</v>
       </c>
       <c r="B92" t="n">
-        <v>0.003574466211980094</v>
+        <v>0.003574239620845665</v>
       </c>
       <c r="C92" t="n">
-        <v>0.3604818255268124</v>
+        <v>0.6104379547257265</v>
       </c>
     </row>
     <row r="93">
@@ -1439,10 +1439,10 @@
         <v>0.8383838383838385</v>
       </c>
       <c r="B93" t="n">
-        <v>0.004375006629637143</v>
+        <v>0.004374712676161707</v>
       </c>
       <c r="C93" t="n">
-        <v>0.395034641618689</v>
+        <v>0.4405428213747329</v>
       </c>
     </row>
     <row r="94">
@@ -1450,10 +1450,10 @@
         <v>0.8585858585858588</v>
       </c>
       <c r="B94" t="n">
-        <v>0.005354349712689384</v>
+        <v>0.005354227258797711</v>
       </c>
       <c r="C94" t="n">
-        <v>0.4522837133447549</v>
+        <v>0.8276842662366212</v>
       </c>
     </row>
     <row r="95">
@@ -1461,10 +1461,10 @@
         <v>0.8787878787878789</v>
       </c>
       <c r="B95" t="n">
-        <v>0.006553247891998884</v>
+        <v>0.006553600602925487</v>
       </c>
       <c r="C95" t="n">
-        <v>0.191644216941365</v>
+        <v>0.9993203536355445</v>
       </c>
     </row>
     <row r="96">
@@ -1472,10 +1472,10 @@
         <v>0.8989898989898992</v>
       </c>
       <c r="B96" t="n">
-        <v>0.008020719470624637</v>
+        <v>0.008020418319870862</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8172002358273067</v>
+        <v>0.2789734881043218</v>
       </c>
     </row>
     <row r="97">
@@ -1483,10 +1483,10 @@
         <v>0.9191919191919193</v>
       </c>
       <c r="B97" t="n">
-        <v>0.009816632102747485</v>
+        <v>0.009816541444036569</v>
       </c>
       <c r="C97" t="n">
-        <v>0.8035571415120484</v>
+        <v>0.01544791187835803</v>
       </c>
     </row>
     <row r="98">
@@ -1494,10 +1494,10 @@
         <v>0.9393939393939394</v>
       </c>
       <c r="B98" t="n">
-        <v>0.01201442071888681</v>
+        <v>0.01201437743063401</v>
       </c>
       <c r="C98" t="n">
-        <v>0.8462221037564674</v>
+        <v>0.8375411683462632</v>
       </c>
     </row>
     <row r="99">
@@ -1505,10 +1505,10 @@
         <v>0.9595959595959598</v>
       </c>
       <c r="B99" t="n">
-        <v>0.0147041960610679</v>
+        <v>0.01470432422679279</v>
       </c>
       <c r="C99" t="n">
-        <v>0.1804739234019467</v>
+        <v>0.6028249406322147</v>
       </c>
     </row>
     <row r="100">
@@ -1516,10 +1516,10 @@
         <v>0.9797979797979799</v>
       </c>
       <c r="B100" t="n">
-        <v>0.01799637038480763</v>
+        <v>0.01799647501880693</v>
       </c>
       <c r="C100" t="n">
-        <v>0.6846487947794674</v>
+        <v>0.1586659484596776</v>
       </c>
     </row>
     <row r="101">
@@ -1527,10 +1527,10 @@
         <v>1</v>
       </c>
       <c r="B101" t="n">
-        <v>0.02202569566643334</v>
+        <v>0.02202543171957973</v>
       </c>
       <c r="C101" t="n">
-        <v>0.586490944965345</v>
+        <v>0.05000589107334086</v>
       </c>
     </row>
   </sheetData>

--- a/datos/valido_A_V.xlsx
+++ b/datos/valido_A_V.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="datos_IV" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,10 +439,10 @@
         <v>-1</v>
       </c>
       <c r="B2" t="n">
-        <v>-7.91382815628556e-07</v>
+        <v>-9.060291313118728e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8597657465422806</v>
+        <v>-9.060291313118728e-07</v>
       </c>
     </row>
     <row r="3">
@@ -449,10 +450,10 @@
         <v>-0.9797979797979798</v>
       </c>
       <c r="B3" t="n">
-        <v>-9.535556356896187e-07</v>
+        <v>-1.025476618804433e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5655009916061121</v>
+        <v>-1.025476618804433e-06</v>
       </c>
     </row>
     <row r="4">
@@ -460,10 +461,10 @@
         <v>-0.9595959595959596</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.131456109963461e-06</v>
+        <v>-9.208350467201674e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9956488281528918</v>
+        <v>-9.208350467201674e-07</v>
       </c>
     </row>
     <row r="5">
@@ -471,10 +472,10 @@
         <v>-0.9393939393939394</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.004443860545327e-06</v>
+        <v>-9.939457122281857e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3657040435596536</v>
+        <v>-9.939457122281857e-07</v>
       </c>
     </row>
     <row r="6">
@@ -482,10 +483,10 @@
         <v>-0.9191919191919192</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.123865225013688e-06</v>
+        <v>-9.880985079129695e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7019497334496633</v>
+        <v>-9.880985079129695e-07</v>
       </c>
     </row>
     <row r="7">
@@ -493,10 +494,10 @@
         <v>-0.898989898989899</v>
       </c>
       <c r="B7" t="n">
-        <v>-9.884863891399779e-07</v>
+        <v>-1.013296012785154e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5409879100332022</v>
+        <v>-1.013296012785154e-06</v>
       </c>
     </row>
     <row r="8">
@@ -504,10 +505,10 @@
         <v>-0.8787878787878788</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.01318190063276e-06</v>
+        <v>-1.032698671638317e-06</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4309893385014196</v>
+        <v>-1.032698671638317e-06</v>
       </c>
     </row>
     <row r="9">
@@ -515,10 +516,10 @@
         <v>-0.8585858585858586</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.003495655064162e-06</v>
+        <v>-8.895579698551899e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3168468471363356</v>
+        <v>-8.895579698551899e-07</v>
       </c>
     </row>
     <row r="10">
@@ -526,10 +527,10 @@
         <v>-0.8383838383838383</v>
       </c>
       <c r="B10" t="n">
-        <v>-9.000748826094709e-07</v>
+        <v>-9.660111508627902e-07</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1998943209466705</v>
+        <v>-9.660111508627902e-07</v>
       </c>
     </row>
     <row r="11">
@@ -537,10 +538,10 @@
         <v>-0.8181818181818181</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.032605925694341e-06</v>
+        <v>-8.210976600543133e-07</v>
       </c>
       <c r="C11" t="n">
-        <v>0.494717919375517</v>
+        <v>-8.210976600543133e-07</v>
       </c>
     </row>
     <row r="12">
@@ -548,10 +549,10 @@
         <v>-0.797979797979798</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.185632518580231e-06</v>
+        <v>-9.505490510980892e-07</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8567564858344039</v>
+        <v>-9.505490510980892e-07</v>
       </c>
     </row>
     <row r="13">
@@ -559,10 +560,10 @@
         <v>-0.7777777777777778</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.088475544188018e-06</v>
+        <v>-1.031043365674793e-06</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9664678332564142</v>
+        <v>-1.031043365674793e-06</v>
       </c>
     </row>
     <row r="14">
@@ -570,10 +571,10 @@
         <v>-0.7575757575757576</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.046282513347392e-06</v>
+        <v>-9.308744898158174e-07</v>
       </c>
       <c r="C14" t="n">
-        <v>0.09707694792436261</v>
+        <v>-9.308744898158174e-07</v>
       </c>
     </row>
     <row r="15">
@@ -581,10 +582,10 @@
         <v>-0.7373737373737373</v>
       </c>
       <c r="B15" t="n">
-        <v>-1.039953389881279e-06</v>
+        <v>-9.679637297540356e-07</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01039690385540026</v>
+        <v>-9.679637297540356e-07</v>
       </c>
     </row>
     <row r="16">
@@ -592,10 +593,10 @@
         <v>-0.7171717171717171</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.058303790315129e-06</v>
+        <v>-9.812205760267943e-07</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3301078506035493</v>
+        <v>-9.812205760267943e-07</v>
       </c>
     </row>
     <row r="17">
@@ -603,10 +604,10 @@
         <v>-0.696969696969697</v>
       </c>
       <c r="B17" t="n">
-        <v>-1.033541358240666e-06</v>
+        <v>-9.24574208443626e-07</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9180238196886684</v>
+        <v>-9.24574208443626e-07</v>
       </c>
     </row>
     <row r="18">
@@ -614,10 +615,10 @@
         <v>-0.6767676767676767</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.006585056017597e-06</v>
+        <v>-9.839757606847289e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1709039759092371</v>
+        <v>-9.839757606847289e-07</v>
       </c>
     </row>
     <row r="19">
@@ -625,10 +626,10 @@
         <v>-0.6565656565656566</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.059339781256684e-06</v>
+        <v>-9.054644640152456e-07</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06317591700204628</v>
+        <v>-9.054644640152456e-07</v>
       </c>
     </row>
     <row r="20">
@@ -636,10 +637,10 @@
         <v>-0.6363636363636364</v>
       </c>
       <c r="B20" t="n">
-        <v>-9.969655743174341e-07</v>
+        <v>-1.01721607108945e-06</v>
       </c>
       <c r="C20" t="n">
-        <v>0.607328476610774</v>
+        <v>-1.01721607108945e-06</v>
       </c>
     </row>
     <row r="21">
@@ -647,10 +648,10 @@
         <v>-0.6161616161616161</v>
       </c>
       <c r="B21" t="n">
-        <v>-8.543447378966739e-07</v>
+        <v>-1.008309129690224e-06</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06855063292951868</v>
+        <v>-1.008309129690224e-06</v>
       </c>
     </row>
     <row r="22">
@@ -658,10 +659,10 @@
         <v>-0.5959595959595959</v>
       </c>
       <c r="B22" t="n">
-        <v>-9.36014181879687e-07</v>
+        <v>-1.062237797263645e-06</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4451886051518361</v>
+        <v>-1.062237797263645e-06</v>
       </c>
     </row>
     <row r="23">
@@ -669,10 +670,10 @@
         <v>-0.5757575757575757</v>
       </c>
       <c r="B23" t="n">
-        <v>-8.601049299330769e-07</v>
+        <v>-9.98053610038243e-07</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6738111832154418</v>
+        <v>-9.98053610038243e-07</v>
       </c>
     </row>
     <row r="24">
@@ -680,10 +681,10 @@
         <v>-0.5555555555555556</v>
       </c>
       <c r="B24" t="n">
-        <v>-1.119439146697948e-06</v>
+        <v>-8.905340417474425e-07</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5525194095288835</v>
+        <v>-8.905340417474425e-07</v>
       </c>
     </row>
     <row r="25">
@@ -691,10 +692,10 @@
         <v>-0.5353535353535352</v>
       </c>
       <c r="B25" t="n">
-        <v>-8.505279430467819e-07</v>
+        <v>-9.874554652345496e-07</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1579124141312841</v>
+        <v>-9.874554652345496e-07</v>
       </c>
     </row>
     <row r="26">
@@ -702,10 +703,10 @@
         <v>-0.5151515151515151</v>
       </c>
       <c r="B26" t="n">
-        <v>-9.48465417546847e-07</v>
+        <v>-1.056849374931016e-06</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9752332546535737</v>
+        <v>-1.056849374931016e-06</v>
       </c>
     </row>
     <row r="27">
@@ -713,10 +714,10 @@
         <v>-0.4949494949494949</v>
       </c>
       <c r="B27" t="n">
-        <v>-8.255663568746406e-07</v>
+        <v>-9.083525478506521e-07</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6846797383111051</v>
+        <v>-9.083525478506521e-07</v>
       </c>
     </row>
     <row r="28">
@@ -724,10 +725,10 @@
         <v>-0.4747474747474747</v>
       </c>
       <c r="B28" t="n">
-        <v>-1.066192118224432e-06</v>
+        <v>-1.083086941707723e-06</v>
       </c>
       <c r="C28" t="n">
-        <v>0.37456112122695</v>
+        <v>-1.083086941707723e-06</v>
       </c>
     </row>
     <row r="29">
@@ -735,10 +736,10 @@
         <v>-0.4545454545454545</v>
       </c>
       <c r="B29" t="n">
-        <v>-8.71602550749342e-07</v>
+        <v>-1.072953231621892e-06</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2490038526117699</v>
+        <v>-1.072953231621892e-06</v>
       </c>
     </row>
     <row r="30">
@@ -746,10 +747,10 @@
         <v>-0.4343434343434343</v>
       </c>
       <c r="B30" t="n">
-        <v>-9.416885733387146e-07</v>
+        <v>-1.164270626579342e-06</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4700082882592929</v>
+        <v>-1.164270626579342e-06</v>
       </c>
     </row>
     <row r="31">
@@ -757,10 +758,10 @@
         <v>-0.4141414141414141</v>
       </c>
       <c r="B31" t="n">
-        <v>-1.140816881680844e-06</v>
+        <v>-9.438003211964303e-07</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9576465876456245</v>
+        <v>-9.438003211964303e-07</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +769,10 @@
         <v>-0.3939393939393939</v>
       </c>
       <c r="B32" t="n">
-        <v>-9.541626860037162e-07</v>
+        <v>-1.071396088968631e-06</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7015172912985294</v>
+        <v>-1.071396088968631e-06</v>
       </c>
     </row>
     <row r="33">
@@ -779,10 +780,10 @@
         <v>-0.3737373737373737</v>
       </c>
       <c r="B33" t="n">
-        <v>-1.139045401304021e-06</v>
+        <v>-1.087653374774563e-06</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9374548021764972</v>
+        <v>-1.087653374774563e-06</v>
       </c>
     </row>
     <row r="34">
@@ -790,10 +791,10 @@
         <v>-0.3535353535353535</v>
       </c>
       <c r="B34" t="n">
-        <v>-8.850531152068297e-07</v>
+        <v>-9.164884757878545e-07</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3257677724655811</v>
+        <v>-9.164884757878545e-07</v>
       </c>
     </row>
     <row r="35">
@@ -801,10 +802,10 @@
         <v>-0.3333333333333333</v>
       </c>
       <c r="B35" t="n">
-        <v>-9.308071163259937e-07</v>
+        <v>-1.104216099219426e-06</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1671781059806727</v>
+        <v>-1.104216099219426e-06</v>
       </c>
     </row>
     <row r="36">
@@ -812,10 +813,10 @@
         <v>-0.313131313131313</v>
       </c>
       <c r="B36" t="n">
-        <v>-9.199858250862126e-07</v>
+        <v>-9.036106209732849e-07</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3896009606275819</v>
+        <v>-9.036106209732849e-07</v>
       </c>
     </row>
     <row r="37">
@@ -823,10 +824,10 @@
         <v>-0.2929292929292928</v>
       </c>
       <c r="B37" t="n">
-        <v>-1.074826770891062e-06</v>
+        <v>-9.044882184288117e-07</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2545174802438227</v>
+        <v>-9.044882184288117e-07</v>
       </c>
     </row>
     <row r="38">
@@ -834,10 +835,10 @@
         <v>-0.2727272727272727</v>
       </c>
       <c r="B38" t="n">
-        <v>-1.016937329730066e-06</v>
+        <v>-8.172279349155059e-07</v>
       </c>
       <c r="C38" t="n">
-        <v>0.6392434461088895</v>
+        <v>-8.172279349155059e-07</v>
       </c>
     </row>
     <row r="39">
@@ -845,10 +846,10 @@
         <v>-0.2525252525252525</v>
       </c>
       <c r="B39" t="n">
-        <v>-8.673856374865777e-07</v>
+        <v>-1.044441138448952e-06</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1266600229626923</v>
+        <v>-1.044441138448952e-06</v>
       </c>
     </row>
     <row r="40">
@@ -856,10 +857,10 @@
         <v>-0.2323232323232323</v>
       </c>
       <c r="B40" t="n">
-        <v>-7.82584376595757e-07</v>
+        <v>-8.176013980001192e-07</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3972461762124689</v>
+        <v>-8.176013980001192e-07</v>
       </c>
     </row>
     <row r="41">
@@ -867,10 +868,10 @@
         <v>-0.212121212121212</v>
       </c>
       <c r="B41" t="n">
-        <v>-7.758090387364335e-07</v>
+        <v>-7.129702080926139e-07</v>
       </c>
       <c r="C41" t="n">
-        <v>0.6929457587636271</v>
+        <v>-7.129702080926139e-07</v>
       </c>
     </row>
     <row r="42">
@@ -878,10 +879,10 @@
         <v>-0.1919191919191918</v>
       </c>
       <c r="B42" t="n">
-        <v>-8.895480824425226e-07</v>
+        <v>-8.840894170126057e-07</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4843620132252346</v>
+        <v>-8.840894170126057e-07</v>
       </c>
     </row>
     <row r="43">
@@ -889,10 +890,10 @@
         <v>-0.1717171717171716</v>
       </c>
       <c r="B43" t="n">
-        <v>-8.175269900738015e-07</v>
+        <v>-9.813553615918022e-07</v>
       </c>
       <c r="C43" t="n">
-        <v>0.5270199758905224</v>
+        <v>-9.813553615918022e-07</v>
       </c>
     </row>
     <row r="44">
@@ -900,10 +901,10 @@
         <v>-0.1515151515151515</v>
       </c>
       <c r="B44" t="n">
-        <v>-7.288944401382436e-07</v>
+        <v>-6.417537643462905e-07</v>
       </c>
       <c r="C44" t="n">
-        <v>0.03428083918255065</v>
+        <v>-6.417537643462905e-07</v>
       </c>
     </row>
     <row r="45">
@@ -911,10 +912,10 @@
         <v>-0.1313131313131313</v>
       </c>
       <c r="B45" t="n">
-        <v>-6.715202624589571e-07</v>
+        <v>-8.477901694546592e-07</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4015712841660963</v>
+        <v>-8.477901694546592e-07</v>
       </c>
     </row>
     <row r="46">
@@ -922,10 +923,10 @@
         <v>-0.111111111111111</v>
       </c>
       <c r="B46" t="n">
-        <v>-5.742423216936066e-07</v>
+        <v>-7.894269556615001e-07</v>
       </c>
       <c r="C46" t="n">
-        <v>0.8527263858048503</v>
+        <v>-7.894269556615001e-07</v>
       </c>
     </row>
     <row r="47">
@@ -933,10 +934,10 @@
         <v>-0.09090909090909083</v>
       </c>
       <c r="B47" t="n">
-        <v>-6.246510214054008e-07</v>
+        <v>-5.033167180612068e-07</v>
       </c>
       <c r="C47" t="n">
-        <v>0.415112063522022</v>
+        <v>-5.033167180612068e-07</v>
       </c>
     </row>
     <row r="48">
@@ -944,10 +945,10 @@
         <v>-0.07070707070707061</v>
       </c>
       <c r="B48" t="n">
-        <v>-2.823514400274572e-07</v>
+        <v>-4.045065881093884e-07</v>
       </c>
       <c r="C48" t="n">
-        <v>0.556244513823373</v>
+        <v>-4.045065881093884e-07</v>
       </c>
     </row>
     <row r="49">
@@ -955,10 +956,10 @@
         <v>-0.05050505050505039</v>
       </c>
       <c r="B49" t="n">
-        <v>-3.446189635583563e-07</v>
+        <v>-3.673348472537768e-07</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8013892896228683</v>
+        <v>-3.673348472537768e-07</v>
       </c>
     </row>
     <row r="50">
@@ -966,10 +967,10 @@
         <v>-0.03030303030303028</v>
       </c>
       <c r="B50" t="n">
-        <v>-1.983740232388145e-07</v>
+        <v>-2.826904693312318e-07</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3388577075917287</v>
+        <v>-2.826904693312318e-07</v>
       </c>
     </row>
     <row r="51">
@@ -977,10 +978,10 @@
         <v>-0.01010101010101006</v>
       </c>
       <c r="B51" t="n">
-        <v>-8.830992649268545e-08</v>
+        <v>-9.991425730360534e-08</v>
       </c>
       <c r="C51" t="n">
-        <v>0.09096822682718064</v>
+        <v>-9.991425730360534e-08</v>
       </c>
     </row>
     <row r="52">
@@ -988,10 +989,10 @@
         <v>0.01010101010101017</v>
       </c>
       <c r="B52" t="n">
-        <v>1.429669107922869e-07</v>
+        <v>-7.668726877212731e-09</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3681495628310731</v>
+        <v>-7.668726877212731e-09</v>
       </c>
     </row>
     <row r="53">
@@ -999,10 +1000,10 @@
         <v>0.0303030303030305</v>
       </c>
       <c r="B53" t="n">
-        <v>4.714843374497352e-07</v>
+        <v>5.550870354910204e-07</v>
       </c>
       <c r="C53" t="n">
-        <v>0.756758935001796</v>
+        <v>5.550870354910204e-07</v>
       </c>
     </row>
     <row r="54">
@@ -1010,10 +1011,10 @@
         <v>0.05050505050505061</v>
       </c>
       <c r="B54" t="n">
-        <v>7.826311561243153e-07</v>
+        <v>5.824544898566159e-07</v>
       </c>
       <c r="C54" t="n">
-        <v>0.5715742839994177</v>
+        <v>5.824544898566159e-07</v>
       </c>
     </row>
     <row r="55">
@@ -1021,10 +1022,10 @@
         <v>0.07070707070707072</v>
       </c>
       <c r="B55" t="n">
-        <v>1.127508592491403e-06</v>
+        <v>1.032307813248672e-06</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7816706896164148</v>
+        <v>1.032307813248672e-06</v>
       </c>
     </row>
     <row r="56">
@@ -1032,10 +1033,10 @@
         <v>0.09090909090909105</v>
       </c>
       <c r="B56" t="n">
-        <v>1.618874982278266e-06</v>
+        <v>1.248489974603125e-06</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8032107108000118</v>
+        <v>1.248489974603125e-06</v>
       </c>
     </row>
     <row r="57">
@@ -1043,10 +1044,10 @@
         <v>0.1111111111111112</v>
       </c>
       <c r="B57" t="n">
-        <v>2.220029517814765e-06</v>
+        <v>1.919746172533789e-06</v>
       </c>
       <c r="C57" t="n">
-        <v>0.5823380218450851</v>
+        <v>1.919746172533789e-06</v>
       </c>
     </row>
     <row r="58">
@@ -1054,10 +1055,10 @@
         <v>0.1313131313131315</v>
       </c>
       <c r="B58" t="n">
-        <v>2.656409118615374e-06</v>
+        <v>2.565377451685101e-06</v>
       </c>
       <c r="C58" t="n">
-        <v>0.01986163574362187</v>
+        <v>2.565377451685101e-06</v>
       </c>
     </row>
     <row r="59">
@@ -1065,10 +1066,10 @@
         <v>0.1515151515151516</v>
       </c>
       <c r="B59" t="n">
-        <v>3.714190637854328e-06</v>
+        <v>3.591487654969404e-06</v>
       </c>
       <c r="C59" t="n">
-        <v>0.2776228956103163</v>
+        <v>3.591487654969404e-06</v>
       </c>
     </row>
     <row r="60">
@@ -1076,10 +1077,10 @@
         <v>0.1717171717171717</v>
       </c>
       <c r="B60" t="n">
-        <v>4.548723875859343e-06</v>
+        <v>4.549291137848661e-06</v>
       </c>
       <c r="C60" t="n">
-        <v>0.204644714746124</v>
+        <v>4.549291137848661e-06</v>
       </c>
     </row>
     <row r="61">
@@ -1087,10 +1088,10 @@
         <v>0.191919191919192</v>
       </c>
       <c r="B61" t="n">
-        <v>5.786113609983416e-06</v>
+        <v>5.755228041825762e-06</v>
       </c>
       <c r="C61" t="n">
-        <v>0.912724830375214</v>
+        <v>5.755228041825762e-06</v>
       </c>
     </row>
     <row r="62">
@@ -1098,10 +1099,10 @@
         <v>0.2121212121212122</v>
       </c>
       <c r="B62" t="n">
-        <v>7.209346273337599e-06</v>
+        <v>7.348111765935121e-06</v>
       </c>
       <c r="C62" t="n">
-        <v>0.3320408056737375</v>
+        <v>7.348111765935121e-06</v>
       </c>
     </row>
     <row r="63">
@@ -1109,10 +1110,10 @@
         <v>0.2323232323232325</v>
       </c>
       <c r="B63" t="n">
-        <v>9.206414237881108e-06</v>
+        <v>9.249040107497012e-06</v>
       </c>
       <c r="C63" t="n">
-        <v>0.4951326004181525</v>
+        <v>9.249040107497012e-06</v>
       </c>
     </row>
     <row r="64">
@@ -1120,10 +1121,10 @@
         <v>0.2525252525252526</v>
       </c>
       <c r="B64" t="n">
-        <v>1.156230839659215e-05</v>
+        <v>1.141499242305858e-05</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1590947244937484</v>
+        <v>1.141499242305858e-05</v>
       </c>
     </row>
     <row r="65">
@@ -1131,10 +1132,10 @@
         <v>0.2727272727272729</v>
       </c>
       <c r="B65" t="n">
-        <v>1.412338935635992e-05</v>
+        <v>1.432316614680669e-05</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7349339632640317</v>
+        <v>1.432316614680669e-05</v>
       </c>
     </row>
     <row r="66">
@@ -1142,10 +1143,10 @@
         <v>0.292929292929293</v>
       </c>
       <c r="B66" t="n">
-        <v>1.782310794917316e-05</v>
+        <v>1.77346108605411e-05</v>
       </c>
       <c r="C66" t="n">
-        <v>0.3036745902764156</v>
+        <v>1.77346108605411e-05</v>
       </c>
     </row>
     <row r="67">
@@ -1153,10 +1154,10 @@
         <v>0.3131313131313131</v>
       </c>
       <c r="B67" t="n">
-        <v>2.174355338043834e-05</v>
+        <v>2.171019351934533e-05</v>
       </c>
       <c r="C67" t="n">
-        <v>0.006755768081217917</v>
+        <v>2.171019351934533e-05</v>
       </c>
     </row>
     <row r="68">
@@ -1164,10 +1165,10 @@
         <v>0.3333333333333335</v>
       </c>
       <c r="B68" t="n">
-        <v>2.70193782797603e-05</v>
+        <v>2.717264751290629e-05</v>
       </c>
       <c r="C68" t="n">
-        <v>0.5702962702790336</v>
+        <v>2.717264751290629e-05</v>
       </c>
     </row>
     <row r="69">
@@ -1175,10 +1176,10 @@
         <v>0.3535353535353536</v>
       </c>
       <c r="B69" t="n">
-        <v>3.340512757349078e-05</v>
+        <v>3.327417460382085e-05</v>
       </c>
       <c r="C69" t="n">
-        <v>0.1430199462240163</v>
+        <v>3.327417460382085e-05</v>
       </c>
     </row>
     <row r="70">
@@ -1186,10 +1187,10 @@
         <v>0.3737373737373739</v>
       </c>
       <c r="B70" t="n">
-        <v>4.095258448956087e-05</v>
+        <v>4.093458982286921e-05</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7172918345969204</v>
+        <v>4.093458982286921e-05</v>
       </c>
     </row>
     <row r="71">
@@ -1197,10 +1198,10 @@
         <v>0.393939393939394</v>
       </c>
       <c r="B71" t="n">
-        <v>5.037597661793206e-05</v>
+        <v>5.04154443250146e-05</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8830115865071336</v>
+        <v>5.04154443250146e-05</v>
       </c>
     </row>
     <row r="72">
@@ -1208,10 +1209,10 @@
         <v>0.4141414141414144</v>
       </c>
       <c r="B72" t="n">
-        <v>6.202513172468231e-05</v>
+        <v>6.185357378646235e-05</v>
       </c>
       <c r="C72" t="n">
-        <v>0.5579769067668255</v>
+        <v>6.185357378646235e-05</v>
       </c>
     </row>
     <row r="73">
@@ -1219,10 +1220,10 @@
         <v>0.4343434343434345</v>
       </c>
       <c r="B73" t="n">
-        <v>7.604588860342151e-05</v>
+        <v>7.581434574901262e-05</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8566704900485425</v>
+        <v>7.581434574901262e-05</v>
       </c>
     </row>
     <row r="74">
@@ -1230,10 +1231,10 @@
         <v>0.4545454545454546</v>
       </c>
       <c r="B74" t="n">
-        <v>9.316761245069294e-05</v>
+        <v>9.335723902500769e-05</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6446452775340766</v>
+        <v>9.335723902500769e-05</v>
       </c>
     </row>
     <row r="75">
@@ -1241,10 +1242,10 @@
         <v>0.4747474747474749</v>
       </c>
       <c r="B75" t="n">
-        <v>0.0001141109558667256</v>
+        <v>0.0001144401918581458</v>
       </c>
       <c r="C75" t="n">
-        <v>0.286852507569956</v>
+        <v>0.0001144401918581458</v>
       </c>
     </row>
     <row r="76">
@@ -1252,10 +1253,10 @@
         <v>0.494949494949495</v>
       </c>
       <c r="B76" t="n">
-        <v>0.0001400139975597575</v>
+        <v>0.0001400562281864338</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8036932903190454</v>
+        <v>0.0001400562281864338</v>
       </c>
     </row>
     <row r="77">
@@ -1263,10 +1264,10 @@
         <v>0.5151515151515154</v>
       </c>
       <c r="B77" t="n">
-        <v>0.0001716564061462679</v>
+        <v>0.0001717325007261581</v>
       </c>
       <c r="C77" t="n">
-        <v>0.1243848018535424</v>
+        <v>0.0001717325007261581</v>
       </c>
     </row>
     <row r="78">
@@ -1274,10 +1275,10 @@
         <v>0.5353535353535355</v>
       </c>
       <c r="B78" t="n">
-        <v>0.0002104265272911884</v>
+        <v>0.0002101740000035529</v>
       </c>
       <c r="C78" t="n">
-        <v>0.1535736524106033</v>
+        <v>0.0002101740000035529</v>
       </c>
     </row>
     <row r="79">
@@ -1285,10 +1286,10 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="B79" t="n">
-        <v>0.0002577169137352468</v>
+        <v>0.0002576652998215516</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0381150762725061</v>
+        <v>0.0002576652998215516</v>
       </c>
     </row>
     <row r="80">
@@ -1296,10 +1297,10 @@
         <v>0.5757575757575759</v>
       </c>
       <c r="B80" t="n">
-        <v>0.0003153731223160003</v>
+        <v>0.0003157107066080777</v>
       </c>
       <c r="C80" t="n">
-        <v>0.05293276426416549</v>
+        <v>0.0003157107066080777</v>
       </c>
     </row>
     <row r="81">
@@ -1307,10 +1308,10 @@
         <v>0.595959595959596</v>
       </c>
       <c r="B81" t="n">
-        <v>0.000386465786532845</v>
+        <v>0.0003865367709437426</v>
       </c>
       <c r="C81" t="n">
-        <v>0.01317163726587223</v>
+        <v>0.0003865367709437426</v>
       </c>
     </row>
     <row r="82">
@@ -1318,10 +1319,10 @@
         <v>0.6161616161616164</v>
       </c>
       <c r="B82" t="n">
-        <v>0.0004731496588571047</v>
+        <v>0.0004730889288792083</v>
       </c>
       <c r="C82" t="n">
-        <v>0.5591079458747207</v>
+        <v>0.0004730889288792083</v>
       </c>
     </row>
     <row r="83">
@@ -1329,10 +1330,10 @@
         <v>0.6363636363636365</v>
       </c>
       <c r="B83" t="n">
-        <v>0.0005794097336626033</v>
+        <v>0.0005794626687332513</v>
       </c>
       <c r="C83" t="n">
-        <v>0.8837469288700445</v>
+        <v>0.0005794626687332513</v>
       </c>
     </row>
     <row r="84">
@@ -1340,10 +1341,10 @@
         <v>0.6565656565656568</v>
       </c>
       <c r="B84" t="n">
-        <v>0.0007091473019052056</v>
+        <v>0.0007093116440814544</v>
       </c>
       <c r="C84" t="n">
-        <v>0.7611968666118378</v>
+        <v>0.0007093116440814544</v>
       </c>
     </row>
     <row r="85">
@@ -1351,10 +1352,10 @@
         <v>0.6767676767676769</v>
       </c>
       <c r="B85" t="n">
-        <v>0.0008683235530685728</v>
+        <v>0.0008681706471194068</v>
       </c>
       <c r="C85" t="n">
-        <v>0.6576139506536023</v>
+        <v>0.0008681706471194068</v>
       </c>
     </row>
     <row r="86">
@@ -1362,10 +1363,10 @@
         <v>0.696969696969697</v>
       </c>
       <c r="B86" t="n">
-        <v>0.001062811176163554</v>
+        <v>0.00106286194662045</v>
       </c>
       <c r="C86" t="n">
-        <v>0.994879194668267</v>
+        <v>0.00106286194662045</v>
       </c>
     </row>
     <row r="87">
@@ -1373,10 +1374,10 @@
         <v>0.7171717171717173</v>
       </c>
       <c r="B87" t="n">
-        <v>0.001301132545570505</v>
+        <v>0.001300966649509705</v>
       </c>
       <c r="C87" t="n">
-        <v>0.9028074875200334</v>
+        <v>0.001300966649509705</v>
       </c>
     </row>
     <row r="88">
@@ -1384,10 +1385,10 @@
         <v>0.7373737373737375</v>
       </c>
       <c r="B88" t="n">
-        <v>0.001592643415091225</v>
+        <v>0.001592527796136433</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0262062647514244</v>
+        <v>0.001592527796136433</v>
       </c>
     </row>
     <row r="89">
@@ -1395,10 +1396,10 @@
         <v>0.7575757575757578</v>
       </c>
       <c r="B89" t="n">
-        <v>0.001949425169978047</v>
+        <v>0.001949322193113534</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5947989578117957</v>
+        <v>0.001949322193113534</v>
       </c>
     </row>
     <row r="90">
@@ -1406,10 +1407,10 @@
         <v>0.7777777777777779</v>
       </c>
       <c r="B90" t="n">
-        <v>0.002385794714233967</v>
+        <v>0.002386073052939303</v>
       </c>
       <c r="C90" t="n">
-        <v>0.9997835024627569</v>
+        <v>0.002386073052939303</v>
       </c>
     </row>
     <row r="91">
@@ -1417,10 +1418,10 @@
         <v>0.7979797979797982</v>
       </c>
       <c r="B91" t="n">
-        <v>0.00292043309995853</v>
+        <v>0.002920310891378682</v>
       </c>
       <c r="C91" t="n">
-        <v>0.4944229140889388</v>
+        <v>0.002920310891378682</v>
       </c>
     </row>
     <row r="92">
@@ -1428,10 +1429,10 @@
         <v>0.8181818181818183</v>
       </c>
       <c r="B92" t="n">
-        <v>0.003574239620845665</v>
+        <v>0.003574110395220754</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6104379547257265</v>
+        <v>0.003574110395220754</v>
       </c>
     </row>
     <row r="93">
@@ -1439,10 +1440,10 @@
         <v>0.8383838383838385</v>
       </c>
       <c r="B93" t="n">
-        <v>0.004374712676161707</v>
+        <v>0.004374902219927328</v>
       </c>
       <c r="C93" t="n">
-        <v>0.4405428213747329</v>
+        <v>0.004374902219927328</v>
       </c>
     </row>
     <row r="94">
@@ -1450,10 +1451,10 @@
         <v>0.8585858585858588</v>
       </c>
       <c r="B94" t="n">
-        <v>0.005354227258797711</v>
+        <v>0.005354073476879308</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8276842662366212</v>
+        <v>0.005354073476879308</v>
       </c>
     </row>
     <row r="95">
@@ -1461,10 +1462,10 @@
         <v>0.8787878787878789</v>
       </c>
       <c r="B95" t="n">
-        <v>0.006553600602925487</v>
+        <v>0.006553389593892936</v>
       </c>
       <c r="C95" t="n">
-        <v>0.9993203536355445</v>
+        <v>0.006553389593892936</v>
       </c>
     </row>
     <row r="96">
@@ -1472,10 +1473,10 @@
         <v>0.8989898989898992</v>
       </c>
       <c r="B96" t="n">
-        <v>0.008020418319870862</v>
+        <v>0.008020794137143714</v>
       </c>
       <c r="C96" t="n">
-        <v>0.2789734881043218</v>
+        <v>0.008020794137143714</v>
       </c>
     </row>
     <row r="97">
@@ -1483,10 +1484,10 @@
         <v>0.9191919191919193</v>
       </c>
       <c r="B97" t="n">
-        <v>0.009816541444036569</v>
+        <v>0.009816603072504922</v>
       </c>
       <c r="C97" t="n">
-        <v>0.01544791187835803</v>
+        <v>0.009816603072504922</v>
       </c>
     </row>
     <row r="98">
@@ -1494,10 +1495,10 @@
         <v>0.9393939393939394</v>
       </c>
       <c r="B98" t="n">
-        <v>0.01201437743063401</v>
+        <v>0.01201439416594192</v>
       </c>
       <c r="C98" t="n">
-        <v>0.8375411683462632</v>
+        <v>0.01201439416594192</v>
       </c>
     </row>
     <row r="99">
@@ -1505,10 +1506,10 @@
         <v>0.9595959595959598</v>
       </c>
       <c r="B99" t="n">
-        <v>0.01470432422679279</v>
+        <v>0.01470428655493628</v>
       </c>
       <c r="C99" t="n">
-        <v>0.6028249406322147</v>
+        <v>0.01470428655493628</v>
       </c>
     </row>
     <row r="100">
@@ -1516,10 +1517,10 @@
         <v>0.9797979797979799</v>
       </c>
       <c r="B100" t="n">
-        <v>0.01799647501880693</v>
+        <v>0.01799629367138017</v>
       </c>
       <c r="C100" t="n">
-        <v>0.1586659484596776</v>
+        <v>0.01799629367138017</v>
       </c>
     </row>
     <row r="101">
@@ -1527,10 +1528,46 @@
         <v>1</v>
       </c>
       <c r="B101" t="n">
-        <v>0.02202543171957973</v>
+        <v>0.02202552944488084</v>
       </c>
       <c r="C101" t="n">
-        <v>0.05000589107334086</v>
+        <v>0.02202552944488084</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fecha y hora inicio</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Isc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:00:00</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>30.5</v>
       </c>
     </row>
   </sheetData>
